--- a/artfynd/S 1685-2024 artfynd.xlsx
+++ b/artfynd/S 1685-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY75"/>
+  <dimension ref="A1:AZ75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/155775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67850804</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/302802</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1117,6 +1137,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/388355</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/388356</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69328727</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69328724</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1705287</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1655,6 +1700,11 @@
           <t>SMF:s mykologivecka</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67850809</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1790,6 +1840,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131617892</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1916,6 +1971,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65809947</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2027,6 +2087,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61093207</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2138,6 +2203,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210321</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2249,6 +2319,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210322</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2360,6 +2435,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2210323</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2466,6 +2546,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2215617</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2577,6 +2662,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2221680</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2686,6 +2776,11 @@
       <c r="AY19" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2223674</t>
         </is>
       </c>
     </row>
@@ -2797,6 +2892,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16460906</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831184</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3010,6 +3115,11 @@
       <c r="AY22" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2909640</t>
         </is>
       </c>
     </row>
@@ -3121,6 +3231,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16460910</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831150</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3339,6 +3459,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831222</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3445,6 +3570,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2633037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2647608</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3667,6 +3802,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2647609</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3778,6 +3918,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2647610</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3887,6 +4032,11 @@
       <c r="AY30" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2654288</t>
         </is>
       </c>
     </row>
@@ -3998,6 +4148,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54652557</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4107,6 +4262,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831152</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4211,6 +4371,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831216</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4320,6 +4485,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831237</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4424,6 +4594,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831155</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4534,6 +4709,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119998</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4643,6 +4823,11 @@
       <c r="AY37" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3385045</t>
         </is>
       </c>
     </row>
@@ -4754,6 +4939,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831195</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4858,6 +5048,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831301</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4964,6 +5159,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3783201</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5070,6 +5270,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3787491</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5176,6 +5381,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3788060</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5287,6 +5497,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3789750</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5396,6 +5611,11 @@
       <c r="AY44" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3789751</t>
         </is>
       </c>
     </row>
@@ -5507,6 +5727,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16460887</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5616,6 +5841,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54652401</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5725,6 +5955,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54652567</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5834,6 +6069,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831187</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5943,6 +6183,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831226</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6047,6 +6292,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831248</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6156,6 +6406,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831282</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6263,6 +6518,11 @@
       <c r="AY52" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831329</t>
         </is>
       </c>
     </row>
@@ -6372,6 +6632,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118958561</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6474,6 +6739,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104684327</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6585,6 +6855,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4757474</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6696,6 +6971,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4757475</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6800,6 +7080,11 @@
       <c r="AY57" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4398963</t>
         </is>
       </c>
     </row>
@@ -6911,6 +7196,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831176</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7017,6 +7307,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4944362</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7123,6 +7418,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5021022</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7227,6 +7527,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5049500</t>
         </is>
       </c>
     </row>
@@ -7338,6 +7643,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831230</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7442,6 +7752,11 @@
       <c r="AY63" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5146483</t>
         </is>
       </c>
     </row>
@@ -7553,6 +7868,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831157</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7662,6 +7982,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831245</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7764,6 +8089,11 @@
       <c r="AY66" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831331</t>
         </is>
       </c>
     </row>
@@ -7873,6 +8203,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118958592</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7977,6 +8312,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60831185</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8081,6 +8421,11 @@
       <c r="AY69" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5922449</t>
         </is>
       </c>
     </row>
@@ -8192,6 +8537,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16460908</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8301,6 +8651,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54652573</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8412,6 +8767,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048595</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8515,6 +8875,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118958569</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8622,6 +8987,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2583497</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8724,8 +9094,89 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6457624</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>